--- a/Output/Models/Exposure_models_malf_card_bin_iqr_Femenino.xlsx
+++ b/Output/Models/Exposure_models_malf_card_bin_iqr_Femenino.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.10301510345373</v>
+        <v>1.108078825116649</v>
       </c>
       <c r="C3">
-        <v>0.2208054360724462</v>
+        <v>0.2199945880772735</v>
       </c>
       <c r="D3">
-        <v>0.4440444718634498</v>
+        <v>0.4665011466582779</v>
       </c>
       <c r="E3">
-        <v>0.6570104314994525</v>
+        <v>0.6408568270088476</v>
       </c>
       <c r="F3">
-        <v>0.715536069935537</v>
+        <v>0.7199642349916517</v>
       </c>
       <c r="G3">
-        <v>1.700322834258588</v>
+        <v>1.705416217912727</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8473917644230938</v>
+        <v>0.8520602041822716</v>
       </c>
       <c r="C4">
-        <v>0.2262745228219606</v>
+        <v>0.220294316325585</v>
       </c>
       <c r="D4">
-        <v>-0.731819726822777</v>
+        <v>-0.7267463597512585</v>
       </c>
       <c r="E4">
-        <v>0.4642786068975596</v>
+        <v>0.4673813481028017</v>
       </c>
       <c r="F4">
-        <v>0.5438498534942953</v>
+        <v>0.5532933109851187</v>
       </c>
       <c r="G4">
-        <v>1.320351192150531</v>
+        <v>1.312155012787894</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9635149920423872</v>
+        <v>0.8587095857802431</v>
       </c>
       <c r="C5">
-        <v>0.2241972799143515</v>
+        <v>0.2308152811905597</v>
       </c>
       <c r="D5">
-        <v>-0.1657791355954452</v>
+        <v>-0.6599411332287428</v>
       </c>
       <c r="E5">
-        <v>0.8683307662872537</v>
+        <v>0.5092916065087889</v>
       </c>
       <c r="F5">
-        <v>0.6208996369476225</v>
+        <v>0.5462305517278321</v>
       </c>
       <c r="G5">
-        <v>1.495187119860976</v>
+        <v>1.34994674021509</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="6">
@@ -812,26 +812,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.9402478979691913</v>
+        <v>0.9149945441625043</v>
       </c>
       <c r="C8">
-        <v>0.2338096548308625</v>
+        <v>0.3371272621036498</v>
       </c>
       <c r="D8">
-        <v>-0.2635122886057523</v>
+        <v>-0.263512288605747</v>
       </c>
       <c r="E8">
-        <v>0.7921557532230109</v>
+        <v>0.792155753223015</v>
       </c>
       <c r="F8">
-        <v>0.5945977098842599</v>
+        <v>0.4725581511906298</v>
       </c>
       <c r="G8">
-        <v>1.486830667086775</v>
+        <v>1.771665590230009</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,26 +875,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B9">
-        <v>1.156263724713089</v>
+        <v>1.249191405147895</v>
       </c>
       <c r="C9">
-        <v>0.2375495127453995</v>
+        <v>0.3437707815300382</v>
       </c>
       <c r="D9">
-        <v>0.6112152288512422</v>
+        <v>0.6472233187700663</v>
       </c>
       <c r="E9">
-        <v>0.5410571027899536</v>
+        <v>0.5174874214231164</v>
       </c>
       <c r="F9">
-        <v>0.7258625481277274</v>
+        <v>0.6368113095626887</v>
       </c>
       <c r="G9">
-        <v>1.841871859260229</v>
+        <v>2.450457683873399</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -938,26 +938,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.8456274935634303</v>
+        <v>0.7782162838275859</v>
       </c>
       <c r="C10">
-        <v>0.2442833014857904</v>
+        <v>0.3518111781041975</v>
       </c>
       <c r="D10">
-        <v>-0.686401118127994</v>
+        <v>-0.7127425427792111</v>
       </c>
       <c r="E10">
-        <v>0.4924601995896792</v>
+        <v>0.4760050858571465</v>
       </c>
       <c r="F10">
-        <v>0.5238956245895851</v>
+        <v>0.3905153382037984</v>
       </c>
       <c r="G10">
-        <v>1.364939549610785</v>
+        <v>1.550824065451591</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1001,26 +1001,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.9671406640843671</v>
+        <v>0.8223494850072548</v>
       </c>
       <c r="C11">
-        <v>0.2375858691739038</v>
+        <v>0.3607252597988556</v>
       </c>
       <c r="D11">
-        <v>-0.1406284381055287</v>
+        <v>-0.542212680501843</v>
       </c>
       <c r="E11">
-        <v>0.8881634811277714</v>
+        <v>0.5876720008107668</v>
       </c>
       <c r="F11">
-        <v>0.607094342055547</v>
+        <v>0.4055146298388914</v>
       </c>
       <c r="G11">
-        <v>1.540717808303949</v>
+        <v>1.667655432703799</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1058,32 +1058,32 @@
         </is>
       </c>
       <c r="O11">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.8147616468706418</v>
+        <v>0.7527884627988205</v>
       </c>
       <c r="C12">
-        <v>0.2036965286896903</v>
+        <v>0.2823587060928054</v>
       </c>
       <c r="D12">
-        <v>-1.005710149606525</v>
+        <v>-1.00571014960651</v>
       </c>
       <c r="E12">
-        <v>0.3145550193963948</v>
+        <v>0.3145550193964017</v>
       </c>
       <c r="F12">
-        <v>0.5465674668648812</v>
+        <v>0.4328413950750724</v>
       </c>
       <c r="G12">
-        <v>1.2145555333162</v>
+        <v>1.309233534894979</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1127,26 +1127,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.9195208021942518</v>
+        <v>0.6834727128644168</v>
       </c>
       <c r="C13">
-        <v>0.2057836979221582</v>
+        <v>0.9334012501875246</v>
       </c>
       <c r="D13">
-        <v>-0.4077223446989582</v>
+        <v>-0.4077223446989259</v>
       </c>
       <c r="E13">
-        <v>0.6834775308683514</v>
+        <v>0.683477530868375</v>
       </c>
       <c r="F13">
-        <v>0.61432495488509</v>
+        <v>0.1097004971546569</v>
       </c>
       <c r="G13">
-        <v>1.376337553837635</v>
+        <v>4.258275589869696</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1190,26 +1190,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.9206675319269616</v>
+        <v>0.8892768598955249</v>
       </c>
       <c r="C14">
-        <v>0.221944216593569</v>
+        <v>0.3150929237571317</v>
       </c>
       <c r="D14">
-        <v>-0.3724192282672614</v>
+        <v>-0.3724192282672384</v>
       </c>
       <c r="E14">
-        <v>0.7095807398134342</v>
+        <v>0.7095807398134513</v>
       </c>
       <c r="F14">
-        <v>0.5959139717941148</v>
+        <v>0.479545045776642</v>
       </c>
       <c r="G14">
-        <v>1.422401125774131</v>
+        <v>1.649090821624258</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1253,26 +1253,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B15">
-        <v>1.128552710952684</v>
+        <v>1.197475948188544</v>
       </c>
       <c r="C15">
-        <v>0.221406627832855</v>
+        <v>0.3181158131005787</v>
       </c>
       <c r="D15">
-        <v>0.5462168239137994</v>
+        <v>0.5665105526339946</v>
       </c>
       <c r="E15">
-        <v>0.5849169028294309</v>
+        <v>0.5710467614049222</v>
       </c>
       <c r="F15">
-        <v>0.731240412639375</v>
+        <v>0.6419277172985193</v>
       </c>
       <c r="G15">
-        <v>1.741740745429461</v>
+        <v>2.23381637503466</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1316,26 +1316,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.8337814180183213</v>
+        <v>0.7788523082138105</v>
       </c>
       <c r="C16">
-        <v>0.2314468976047592</v>
+        <v>0.3284172170355646</v>
       </c>
       <c r="D16">
-        <v>-0.7854242228475156</v>
+        <v>-0.7610253958425588</v>
       </c>
       <c r="E16">
-        <v>0.4322048832270767</v>
+        <v>0.4466418987023424</v>
       </c>
       <c r="F16">
-        <v>0.5297174205892109</v>
+        <v>0.4091719646290135</v>
       </c>
       <c r="G16">
-        <v>1.31238170770252</v>
+        <v>1.482532945677205</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1379,26 +1379,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B17">
-        <v>0.99261882489914</v>
+        <v>0.8461075178159254</v>
       </c>
       <c r="C17">
-        <v>0.2237840357804886</v>
+        <v>0.3403215735397048</v>
       </c>
       <c r="D17">
-        <v>-0.03310580551854648</v>
+        <v>-0.4910321614233059</v>
       </c>
       <c r="E17">
-        <v>0.973590213154806</v>
+        <v>0.6234037006723654</v>
       </c>
       <c r="F17">
-        <v>0.6401727602199037</v>
+        <v>0.4342534778035915</v>
       </c>
       <c r="G17">
-        <v>1.539103493259687</v>
+        <v>1.648571556238451</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1436,32 +1436,32 @@
         </is>
       </c>
       <c r="O17">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.8312262526106157</v>
+        <v>0.7722621679696818</v>
       </c>
       <c r="C18">
-        <v>0.1875459780081153</v>
+        <v>0.2621957089102351</v>
       </c>
       <c r="D18">
-        <v>-0.9856423351298785</v>
+        <v>-0.9856423351298802</v>
       </c>
       <c r="E18">
-        <v>0.3243086557462183</v>
+        <v>0.3243086557462175</v>
       </c>
       <c r="F18">
-        <v>0.5755457153752306</v>
+        <v>0.4619376576503825</v>
       </c>
       <c r="G18">
-        <v>1.20049035996841</v>
+        <v>1.29105918558519</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1505,26 +1505,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.9224316939439472</v>
+        <v>0.7057510300775117</v>
       </c>
       <c r="C19">
-        <v>0.1957102475972864</v>
+        <v>0.8447108668179804</v>
       </c>
       <c r="D19">
-        <v>-0.4125586232982231</v>
+        <v>-0.4125586232982092</v>
       </c>
       <c r="E19">
-        <v>0.6799300215068318</v>
+        <v>0.679930021506842</v>
       </c>
       <c r="F19">
-        <v>0.6285579905625025</v>
+        <v>0.1347821336990882</v>
       </c>
       <c r="G19">
-        <v>1.35370203349231</v>
+        <v>3.695478790738555</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.002029428496944</v>
+        <v>1.003720740035691</v>
       </c>
       <c r="C21">
-        <v>0.1934716424245505</v>
+        <v>0.1937074400057883</v>
       </c>
       <c r="D21">
-        <v>0.01047891031167276</v>
+        <v>0.01917239319491884</v>
       </c>
       <c r="E21">
-        <v>0.9916391922618765</v>
+        <v>0.9847035805931985</v>
       </c>
       <c r="F21">
-        <v>0.685799423763791</v>
+        <v>0.686639567985437</v>
       </c>
       <c r="G21">
-        <v>1.464076726783222</v>
+        <v>1.467225850286511</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.7830160555288146</v>
+        <v>0.771607017563631</v>
       </c>
       <c r="C22">
-        <v>0.2061833010315086</v>
+        <v>0.2068571544774928</v>
       </c>
       <c r="D22">
-        <v>-1.186333116370199</v>
+        <v>-1.253424875857794</v>
       </c>
       <c r="E22">
-        <v>0.2354907734666738</v>
+        <v>0.2100511231089281</v>
       </c>
       <c r="F22">
-        <v>0.5227176001132227</v>
+        <v>0.5144214150037367</v>
       </c>
       <c r="G22">
-        <v>1.172935717265118</v>
+        <v>1.157372870157664</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.8094151461990129</v>
+        <v>0.7341645258243357</v>
       </c>
       <c r="C23">
-        <v>0.2046738422589895</v>
+        <v>0.2129725642449556</v>
       </c>
       <c r="D23">
-        <v>-1.033074532188563</v>
+        <v>-1.450995000020427</v>
       </c>
       <c r="E23">
-        <v>0.3015690206411307</v>
+        <v>0.1467812524935241</v>
       </c>
       <c r="F23">
-        <v>0.5419417838143402</v>
+        <v>0.4836273139022119</v>
       </c>
       <c r="G23">
-        <v>1.20889899701997</v>
+        <v>1.114489474611964</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="24">
@@ -1946,26 +1946,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.9451981221393668</v>
+        <v>0.9233755637621162</v>
       </c>
       <c r="C26">
-        <v>0.2233058960891221</v>
+        <v>0.3158542783120082</v>
       </c>
       <c r="D26">
-        <v>-0.2523924419017605</v>
+        <v>-0.252392441901755</v>
       </c>
       <c r="E26">
-        <v>0.8007377415792623</v>
+        <v>0.8007377415792665</v>
       </c>
       <c r="F26">
-        <v>0.6101611146724468</v>
+        <v>0.4971903926489292</v>
       </c>
       <c r="G26">
-        <v>1.464202599300989</v>
+        <v>1.714881148870169</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2009,26 +2009,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B27">
-        <v>1.143306502160841</v>
+        <v>1.22313517713902</v>
       </c>
       <c r="C27">
-        <v>0.2222276762144032</v>
+        <v>0.3194798372092501</v>
       </c>
       <c r="D27">
-        <v>0.6026454806077199</v>
+        <v>0.630454120351488</v>
       </c>
       <c r="E27">
-        <v>0.5467445576211785</v>
+        <v>0.5283975112542494</v>
       </c>
       <c r="F27">
-        <v>0.7396089066551771</v>
+        <v>0.653932204999136</v>
       </c>
       <c r="G27">
-        <v>1.767352645595816</v>
+        <v>2.287790156407543</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2072,26 +2072,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.8111092205311523</v>
+        <v>0.7220926014261774</v>
       </c>
       <c r="C28">
-        <v>0.2325069749021512</v>
+        <v>0.3318176809132763</v>
       </c>
       <c r="D28">
-        <v>-0.900414106392717</v>
+        <v>-0.9812674556533132</v>
       </c>
       <c r="E28">
-        <v>0.3678999165551845</v>
+        <v>0.3264608670495633</v>
       </c>
       <c r="F28">
-        <v>0.5142437742442982</v>
+        <v>0.3768332129042186</v>
       </c>
       <c r="G28">
-        <v>1.27935076821778</v>
+        <v>1.383683038487787</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2135,26 +2135,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.8888183444744763</v>
+        <v>0.7488163213440776</v>
       </c>
       <c r="C29">
-        <v>0.2284994322444276</v>
+        <v>0.3424134035868553</v>
       </c>
       <c r="D29">
-        <v>-0.5158104775765329</v>
+        <v>-0.844772880849436</v>
       </c>
       <c r="E29">
-        <v>0.6059867839650281</v>
+        <v>0.3982376588038473</v>
       </c>
       <c r="F29">
-        <v>0.5679550169209127</v>
+        <v>0.3827476071313365</v>
       </c>
       <c r="G29">
-        <v>1.390951793607196</v>
+        <v>1.465001668629292</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2192,32 +2192,32 @@
         </is>
       </c>
       <c r="O29">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.7670133975804793</v>
+        <v>0.7054591642812974</v>
       </c>
       <c r="C30">
-        <v>0.2080598844213939</v>
+        <v>0.273678216649631</v>
       </c>
       <c r="D30">
-        <v>-1.274878196701325</v>
+        <v>-1.274878196701317</v>
       </c>
       <c r="E30">
-        <v>0.2023523574339095</v>
+        <v>0.2023523574339126</v>
       </c>
       <c r="F30">
-        <v>0.5101548916019769</v>
+        <v>0.4125879683632679</v>
       </c>
       <c r="G30">
-        <v>1.153197904700186</v>
+        <v>1.20622187419262</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2261,26 +2261,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.8585147360152012</v>
+        <v>0.5152869049745092</v>
       </c>
       <c r="C31">
-        <v>0.1852072409878154</v>
+        <v>0.8049627580876062</v>
       </c>
       <c r="D31">
-        <v>-0.823679641995671</v>
+        <v>-0.8236796419956924</v>
       </c>
       <c r="E31">
-        <v>0.4101216098508855</v>
+        <v>0.4101216098508733</v>
       </c>
       <c r="F31">
-        <v>0.5971714887718795</v>
+        <v>0.1063808764172364</v>
       </c>
       <c r="G31">
-        <v>1.234230980234899</v>
+        <v>2.495942911739237</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2324,26 +2324,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.8419808852692447</v>
+        <v>0.8337792300872628</v>
       </c>
       <c r="C32">
-        <v>0.207335426093894</v>
+        <v>0.219135190094696</v>
       </c>
       <c r="D32">
-        <v>-0.8295638126987203</v>
+        <v>-0.8295638126987132</v>
       </c>
       <c r="E32">
-        <v>0.406785443781906</v>
+        <v>0.4067854437819101</v>
       </c>
       <c r="F32">
-        <v>0.5608129034949796</v>
+        <v>0.5426538148254125</v>
       </c>
       <c r="G32">
-        <v>1.264114657028621</v>
+        <v>1.281088947561478</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2387,26 +2387,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B33">
-        <v>1.046210392984666</v>
+        <v>1.051019241711702</v>
       </c>
       <c r="C33">
-        <v>0.2022551718888378</v>
+        <v>0.2146273398080962</v>
       </c>
       <c r="D33">
-        <v>0.2233539222533707</v>
+        <v>0.2318455783649879</v>
       </c>
       <c r="E33">
-        <v>0.8232600631673955</v>
+        <v>0.8166579549641054</v>
       </c>
       <c r="F33">
-        <v>0.7038159676034964</v>
+        <v>0.6901119443298878</v>
       </c>
       <c r="G33">
-        <v>1.555173847669453</v>
+        <v>1.600669942788585</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2450,26 +2450,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.7798541269240491</v>
+        <v>0.7577935447746529</v>
       </c>
       <c r="C34">
-        <v>0.2155644094833501</v>
+        <v>0.2269549801899028</v>
       </c>
       <c r="D34">
-        <v>-1.153476096301325</v>
+        <v>-1.222023410007885</v>
       </c>
       <c r="E34">
-        <v>0.2487150233708671</v>
+        <v>0.2216987743444407</v>
       </c>
       <c r="F34">
-        <v>0.5111220496973722</v>
+        <v>0.485698175489003</v>
       </c>
       <c r="G34">
-        <v>1.189877172469004</v>
+        <v>1.182320802263619</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2513,26 +2513,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.838046109631187</v>
+        <v>0.7544306911674851</v>
       </c>
       <c r="C35">
-        <v>0.2113851510631092</v>
+        <v>0.2402541977798263</v>
       </c>
       <c r="D35">
-        <v>-0.8358305003874243</v>
+        <v>-1.172890497692474</v>
       </c>
       <c r="E35">
-        <v>0.403250265243021</v>
+        <v>0.2408397206076992</v>
       </c>
       <c r="F35">
-        <v>0.5537790826532387</v>
+        <v>0.4711016266576068</v>
       </c>
       <c r="G35">
-        <v>1.268233676329992</v>
+        <v>1.208158994936171</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2570,32 +2570,32 @@
         </is>
       </c>
       <c r="O35">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.7721367061252595</v>
+        <v>0.7680036931611177</v>
       </c>
       <c r="C36">
-        <v>0.1854912425091044</v>
+        <v>0.1893410855461731</v>
       </c>
       <c r="D36">
-        <v>-1.394101741209861</v>
+        <v>-1.394101741209879</v>
       </c>
       <c r="E36">
-        <v>0.1632868834697277</v>
+        <v>0.1632868834697223</v>
       </c>
       <c r="F36">
-        <v>0.5367891966856186</v>
+        <v>0.5299023972606842</v>
       </c>
       <c r="G36">
-        <v>1.110668949053271</v>
+        <v>1.113091157462628</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,26 +2639,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.7853444727961389</v>
+        <v>0.5084834203918308</v>
       </c>
       <c r="C37">
-        <v>0.1759315791862966</v>
+        <v>0.4924269229159143</v>
       </c>
       <c r="D37">
-        <v>-1.373447789882617</v>
+        <v>-1.373447789882618</v>
       </c>
       <c r="E37">
-        <v>0.1696131816228711</v>
+        <v>0.1696131816228706</v>
       </c>
       <c r="F37">
-        <v>0.5562973099335826</v>
+        <v>0.1936967082279064</v>
       </c>
       <c r="G37">
-        <v>1.108698406298392</v>
+        <v>1.334846581435732</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.8442414095869397</v>
+        <v>0.8987826451573787</v>
       </c>
       <c r="C39">
-        <v>0.5034379961019995</v>
+        <v>0.5042155648745258</v>
       </c>
       <c r="D39">
-        <v>-0.3363210490263995</v>
+        <v>-0.2116437000266167</v>
       </c>
       <c r="E39">
-        <v>0.7366287786567676</v>
+        <v>0.8323850138286056</v>
       </c>
       <c r="F39">
-        <v>0.3147309488472077</v>
+        <v>0.3345535256381784</v>
       </c>
       <c r="G39">
-        <v>2.264612235536322</v>
+        <v>2.414591930230459</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.027116684344976</v>
+        <v>1.290057888263873</v>
       </c>
       <c r="C40">
-        <v>0.5307688571851964</v>
+        <v>0.4918350458883109</v>
       </c>
       <c r="D40">
-        <v>0.05040902612232483</v>
+        <v>0.517830305341312</v>
       </c>
       <c r="E40">
-        <v>0.9597964437270592</v>
+        <v>0.6045766720027974</v>
       </c>
       <c r="F40">
-        <v>0.3629347173101193</v>
+        <v>0.4919924617341364</v>
       </c>
       <c r="G40">
-        <v>2.906772576287791</v>
+        <v>3.382672468610246</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>2.528352598535005</v>
+        <v>1.722928311945347</v>
       </c>
       <c r="C41">
-        <v>0.5019800095948749</v>
+        <v>0.5193441612612703</v>
       </c>
       <c r="D41">
-        <v>1.847818490970891</v>
+        <v>1.047523763099592</v>
       </c>
       <c r="E41">
-        <v>0.06462860501108122</v>
+        <v>0.2948580782072382</v>
       </c>
       <c r="F41">
-        <v>0.9452604358758729</v>
+        <v>0.6225878715398984</v>
       </c>
       <c r="G41">
-        <v>6.762757246467632</v>
+        <v>4.767972689157354</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="42">
@@ -3080,26 +3080,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.5173205508194371</v>
+        <v>0.3866105325129933</v>
       </c>
       <c r="C44">
-        <v>0.5351655926455565</v>
+        <v>0.7716486778580142</v>
       </c>
       <c r="D44">
-        <v>-1.231567546078109</v>
+        <v>-1.231567546078148</v>
       </c>
       <c r="E44">
-        <v>0.2181106703292916</v>
+        <v>0.2181106703292771</v>
       </c>
       <c r="F44">
-        <v>0.1812282734541412</v>
+        <v>0.0852010870910451</v>
       </c>
       <c r="G44">
-        <v>1.476704198519254</v>
+        <v>1.754293389358523</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3143,26 +3143,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B45">
-        <v>0.8381653896426547</v>
+        <v>0.8959382827827971</v>
       </c>
       <c r="C45">
-        <v>0.554373585658566</v>
+        <v>0.8033951597492078</v>
       </c>
       <c r="D45">
-        <v>-0.3184492194404409</v>
+        <v>-0.1367742235796795</v>
       </c>
       <c r="E45">
-        <v>0.7501442081653484</v>
+        <v>0.8912092587408967</v>
       </c>
       <c r="F45">
-        <v>0.2827782952138643</v>
+        <v>0.1855354467358731</v>
       </c>
       <c r="G45">
-        <v>2.48435340436404</v>
+        <v>4.326426139467101</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3206,26 +3206,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B46">
-        <v>1.076766465390555</v>
+        <v>1.399830419598242</v>
       </c>
       <c r="C46">
-        <v>0.5890002909009826</v>
+        <v>0.7868245938429606</v>
       </c>
       <c r="D46">
-        <v>0.1255730051862261</v>
+        <v>0.4274791396432286</v>
       </c>
       <c r="E46">
-        <v>0.9000699325150808</v>
+        <v>0.6690303758600111</v>
       </c>
       <c r="F46">
-        <v>0.3394404268876583</v>
+        <v>0.2994533103228275</v>
       </c>
       <c r="G46">
-        <v>3.415698099429374</v>
+        <v>6.543675211070838</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3269,26 +3269,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B47">
-        <v>2.452275701129287</v>
+        <v>2.581369047325122</v>
       </c>
       <c r="C47">
-        <v>0.5332928454006272</v>
+        <v>0.8180145653645253</v>
       </c>
       <c r="D47">
-        <v>1.682033537062137</v>
+        <v>1.159294634650204</v>
       </c>
       <c r="E47">
-        <v>0.09256233687518407</v>
+        <v>0.2463361080084884</v>
       </c>
       <c r="F47">
-        <v>0.8622428502580053</v>
+        <v>0.519463261319879</v>
       </c>
       <c r="G47">
-        <v>6.974434305311658</v>
+        <v>12.82759851304466</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,32 +3326,32 @@
         </is>
       </c>
       <c r="O47">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B48">
-        <v>0.8882692311461542</v>
+        <v>0.8485431271620794</v>
       </c>
       <c r="C48">
-        <v>0.3570170887913157</v>
+        <v>0.4948875854320753</v>
       </c>
       <c r="D48">
-        <v>-0.3318619680522719</v>
+        <v>-0.3318619680523091</v>
       </c>
       <c r="E48">
-        <v>0.7399934894992723</v>
+        <v>0.7399934894992444</v>
       </c>
       <c r="F48">
-        <v>0.4412158667161212</v>
+        <v>0.3216805804669749</v>
       </c>
       <c r="G48">
-        <v>1.788290690617066</v>
+        <v>2.238324233339668</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,26 +3395,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B49">
-        <v>1.457335029983228</v>
+        <v>5.519233255942779</v>
       </c>
       <c r="C49">
-        <v>0.4288540722484062</v>
+        <v>1.945212041704543</v>
       </c>
       <c r="D49">
-        <v>0.878176214781867</v>
+        <v>0.8781762147818577</v>
       </c>
       <c r="E49">
-        <v>0.3798480976773841</v>
+        <v>0.3798480976773891</v>
       </c>
       <c r="F49">
-        <v>0.6288081414393353</v>
+        <v>0.121930191809163</v>
       </c>
       <c r="G49">
-        <v>3.377541176160352</v>
+        <v>249.8309506572557</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3458,26 +3458,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B50">
-        <v>0.5386342280551056</v>
+        <v>0.4154507695832002</v>
       </c>
       <c r="C50">
-        <v>0.4949985153272777</v>
+        <v>0.7027465362412648</v>
       </c>
       <c r="D50">
-        <v>-1.24994021480684</v>
+        <v>-1.24994021480681</v>
       </c>
       <c r="E50">
-        <v>0.211321387571465</v>
+        <v>0.2113213875714758</v>
       </c>
       <c r="F50">
-        <v>0.2041504998000388</v>
+        <v>0.1047950168090895</v>
       </c>
       <c r="G50">
-        <v>1.421141912053572</v>
+        <v>1.647018600719407</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3521,26 +3521,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B51">
-        <v>0.878460121794978</v>
+        <v>0.9069310395547036</v>
       </c>
       <c r="C51">
-        <v>0.4973530330762013</v>
+        <v>0.7197143470431413</v>
       </c>
       <c r="D51">
-        <v>-0.2605488602355262</v>
+        <v>-0.1357328272262911</v>
       </c>
       <c r="E51">
-        <v>0.7944404312949952</v>
+        <v>0.8920324954942824</v>
       </c>
       <c r="F51">
-        <v>0.3314166949128623</v>
+        <v>0.2212851666351791</v>
       </c>
       <c r="G51">
-        <v>2.32846503338326</v>
+        <v>3.717031389925136</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3584,26 +3584,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B52">
-        <v>0.9732322371471336</v>
+        <v>1.365539767382753</v>
       </c>
       <c r="C52">
-        <v>0.5310714280577435</v>
+        <v>0.717850483699019</v>
       </c>
       <c r="D52">
-        <v>-0.05109019671104532</v>
+        <v>0.4340037257454545</v>
       </c>
       <c r="E52">
-        <v>0.9592536476836502</v>
+        <v>0.6642857355254321</v>
       </c>
       <c r="F52">
-        <v>0.34369060996513</v>
+        <v>0.3344020357967491</v>
       </c>
       <c r="G52">
-        <v>2.755911741430797</v>
+        <v>5.576218613205799</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3647,26 +3647,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B53">
-        <v>2.591779303376438</v>
+        <v>2.456395056071592</v>
       </c>
       <c r="C53">
-        <v>0.4907010378008304</v>
+        <v>0.7466485115811444</v>
       </c>
       <c r="D53">
-        <v>1.940783809691485</v>
+        <v>1.203638441461011</v>
       </c>
       <c r="E53">
-        <v>0.05228450562048843</v>
+        <v>0.2287293547008082</v>
       </c>
       <c r="F53">
-        <v>0.9906324200201388</v>
+        <v>0.5685253697539284</v>
       </c>
       <c r="G53">
-        <v>6.780840018615479</v>
+        <v>10.61320565888655</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3704,32 +3704,32 @@
         </is>
       </c>
       <c r="O53">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B54">
-        <v>0.9335894716287503</v>
+        <v>0.9083997127078751</v>
       </c>
       <c r="C54">
-        <v>0.3061826129621802</v>
+        <v>0.4280537930711222</v>
       </c>
       <c r="D54">
-        <v>-0.2244362427515899</v>
+        <v>-0.2244362427516618</v>
       </c>
       <c r="E54">
-        <v>0.8224178722581366</v>
+        <v>0.8224178722580807</v>
       </c>
       <c r="F54">
-        <v>0.5123099995222935</v>
+        <v>0.3925698472252825</v>
       </c>
       <c r="G54">
-        <v>1.701292776539142</v>
+        <v>2.102020936860699</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3773,26 +3773,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B55">
-        <v>1.521592446710798</v>
+        <v>6.121013628594005</v>
       </c>
       <c r="C55">
-        <v>0.4117724972676733</v>
+        <v>1.77726361991279</v>
       </c>
       <c r="D55">
-        <v>1.019391658107515</v>
+        <v>1.019391658107528</v>
       </c>
       <c r="E55">
-        <v>0.3080170648600181</v>
+        <v>0.3080170648600116</v>
       </c>
       <c r="F55">
-        <v>0.6788861654886161</v>
+        <v>0.1879376579743383</v>
       </c>
       <c r="G55">
-        <v>3.410356097359854</v>
+        <v>199.3576393643758</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.7392503702700477</v>
+        <v>0.7603525836376293</v>
       </c>
       <c r="C57">
-        <v>0.3516499816439341</v>
+        <v>0.3500561160075558</v>
       </c>
       <c r="D57">
-        <v>-0.8591458414549784</v>
+        <v>-0.7826545942627705</v>
       </c>
       <c r="E57">
-        <v>0.3902600587858229</v>
+        <v>0.43382997266568</v>
       </c>
       <c r="F57">
-        <v>0.3710791419280977</v>
+        <v>0.3828659284369549</v>
       </c>
       <c r="G57">
-        <v>1.472707700855613</v>
+        <v>1.510022199689199</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.7534207742628241</v>
+        <v>0.8243830555130848</v>
       </c>
       <c r="C58">
-        <v>0.3763601006312628</v>
+        <v>0.3644236753472935</v>
       </c>
       <c r="D58">
-        <v>-0.7522885917358476</v>
+        <v>-0.5299325948381376</v>
       </c>
       <c r="E58">
-        <v>0.4518775269415586</v>
+        <v>0.5961586660122524</v>
       </c>
       <c r="F58">
-        <v>0.3603124697244404</v>
+        <v>0.4035813249766017</v>
       </c>
       <c r="G58">
-        <v>1.575418312679866</v>
+        <v>1.683941699374943</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.9789471854019598</v>
+        <v>0.7759728261488881</v>
       </c>
       <c r="C59">
-        <v>0.3486390651513638</v>
+        <v>0.3757180912348751</v>
       </c>
       <c r="D59">
-        <v>-0.06103041090088926</v>
+        <v>-0.6750746987662894</v>
       </c>
       <c r="E59">
-        <v>0.9513349897932363</v>
+        <v>0.4996283074464736</v>
       </c>
       <c r="F59">
-        <v>0.4943074451861338</v>
+        <v>0.3715649105846057</v>
       </c>
       <c r="G59">
-        <v>1.938748042618603</v>
+        <v>1.620534689279778</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="60">
@@ -4214,26 +4214,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B62">
-        <v>0.5848288014280637</v>
+        <v>0.4682465622935372</v>
       </c>
       <c r="C62">
-        <v>0.4709896680413545</v>
+        <v>0.666189761654311</v>
       </c>
       <c r="D62">
-        <v>-1.138955179085208</v>
+        <v>-1.138955179085213</v>
       </c>
       <c r="E62">
-        <v>0.2547218490560581</v>
+        <v>0.2547218490560559</v>
       </c>
       <c r="F62">
-        <v>0.2323387348503315</v>
+        <v>0.1268857480598988</v>
       </c>
       <c r="G62">
-        <v>1.472095159681883</v>
+        <v>1.72797060703943</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4277,26 +4277,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B63">
-        <v>0.886643879577153</v>
+        <v>0.9321254282319534</v>
       </c>
       <c r="C63">
-        <v>0.4761936802765325</v>
+        <v>0.6817107586460444</v>
       </c>
       <c r="D63">
-        <v>-0.2526532184549242</v>
+        <v>-0.1031051553934039</v>
       </c>
       <c r="E63">
-        <v>0.8005362014171298</v>
+        <v>0.9178795134207741</v>
       </c>
       <c r="F63">
-        <v>0.3486682684757068</v>
+        <v>0.2450197575755759</v>
       </c>
       <c r="G63">
-        <v>2.254685729299162</v>
+        <v>3.546072457804163</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,26 +4340,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B64">
-        <v>0.8275393168342664</v>
+        <v>0.8762089803854861</v>
       </c>
       <c r="C64">
-        <v>0.5105775960361378</v>
+        <v>0.6871445031036577</v>
       </c>
       <c r="D64">
-        <v>-0.3707539491324712</v>
+        <v>-0.1923185790126754</v>
       </c>
       <c r="E64">
-        <v>0.7108208038357879</v>
+        <v>0.8474926660873632</v>
       </c>
       <c r="F64">
-        <v>0.3042175040329012</v>
+        <v>0.2278815887162687</v>
       </c>
       <c r="G64">
-        <v>2.251091116809836</v>
+        <v>3.36903995462343</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4403,26 +4403,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B65">
-        <v>1.457518425876523</v>
+        <v>1.354083190732803</v>
       </c>
       <c r="C65">
-        <v>0.4649229244608046</v>
+        <v>0.7124986284526394</v>
       </c>
       <c r="D65">
-        <v>0.8103177138669625</v>
+        <v>0.4254388727448545</v>
       </c>
       <c r="E65">
-        <v>0.4177575970734142</v>
+        <v>0.6705167734910319</v>
       </c>
       <c r="F65">
-        <v>0.5859640108301054</v>
+        <v>0.3350930456609897</v>
       </c>
       <c r="G65">
-        <v>3.625410302520296</v>
+        <v>5.471737808847589</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4460,32 +4460,32 @@
         </is>
       </c>
       <c r="O65">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B66">
-        <v>0.7447918269104224</v>
+        <v>0.6786987042096493</v>
       </c>
       <c r="C66">
-        <v>0.3640765491367201</v>
+        <v>0.4788997214373346</v>
       </c>
       <c r="D66">
-        <v>-0.8093092711247196</v>
+        <v>-0.8093092711247171</v>
       </c>
       <c r="E66">
-        <v>0.4183372747778418</v>
+        <v>0.4183372747778432</v>
       </c>
       <c r="F66">
-        <v>0.3648651482412128</v>
+        <v>0.2654830742716055</v>
       </c>
       <c r="G66">
-        <v>1.520328450405578</v>
+        <v>1.735070803890881</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4529,26 +4529,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B67">
-        <v>0.9770992826301585</v>
+        <v>0.9042129784483163</v>
       </c>
       <c r="C67">
-        <v>0.3023787619524521</v>
+        <v>1.314223142195477</v>
       </c>
       <c r="D67">
-        <v>-0.07661587098625515</v>
+        <v>-0.07661587098624342</v>
       </c>
       <c r="E67">
-        <v>0.9389291328443343</v>
+        <v>0.9389291328443437</v>
       </c>
       <c r="F67">
-        <v>0.5401985643081937</v>
+        <v>0.06880214363369129</v>
       </c>
       <c r="G67">
-        <v>1.767355693251496</v>
+        <v>11.88336681408294</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4592,26 +4592,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B68">
-        <v>0.4524602225218789</v>
+        <v>0.4324928968300996</v>
       </c>
       <c r="C68">
-        <v>0.4079446403972953</v>
+        <v>0.4311613697945202</v>
       </c>
       <c r="D68">
-        <v>-1.944027074268611</v>
+        <v>-1.944027074268619</v>
       </c>
       <c r="E68">
-        <v>0.05189218630080846</v>
+        <v>0.05189218630080754</v>
       </c>
       <c r="F68">
-        <v>0.2033936065810379</v>
+        <v>0.1857692192098326</v>
       </c>
       <c r="G68">
-        <v>1.006522556956488</v>
+        <v>1.00689504216095</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4655,26 +4655,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B69">
-        <v>0.755460058273041</v>
+        <v>0.7694047986328055</v>
       </c>
       <c r="C69">
-        <v>0.38916250977033</v>
+        <v>0.4116541093037599</v>
       </c>
       <c r="D69">
-        <v>-0.7205945063159749</v>
+        <v>-0.6367920200680408</v>
       </c>
       <c r="E69">
-        <v>0.4711590348719277</v>
+        <v>0.5242603246748641</v>
       </c>
       <c r="F69">
-        <v>0.3523349934939681</v>
+        <v>0.3433636188218464</v>
       </c>
       <c r="G69">
-        <v>1.619821789446177</v>
+        <v>1.724072416846054</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4718,26 +4718,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B70">
-        <v>0.7254583523384289</v>
+        <v>0.7937083283294391</v>
       </c>
       <c r="C70">
-        <v>0.4156950730072832</v>
+        <v>0.4209144925276782</v>
       </c>
       <c r="D70">
-        <v>-0.7720842381995177</v>
+        <v>-0.5488982536771216</v>
       </c>
       <c r="E70">
-        <v>0.4400645368975966</v>
+        <v>0.5830752766868087</v>
       </c>
       <c r="F70">
-        <v>0.3211975304627752</v>
+        <v>0.3478386779420687</v>
       </c>
       <c r="G70">
-        <v>1.63852387102516</v>
+        <v>1.811106557173703</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4781,26 +4781,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B71">
-        <v>1.057927866881138</v>
+        <v>0.8568112532233184</v>
       </c>
       <c r="C71">
-        <v>0.3753438007367764</v>
+        <v>0.4457918598626522</v>
       </c>
       <c r="D71">
-        <v>0.150028193485562</v>
+        <v>-0.3466586984524962</v>
       </c>
       <c r="E71">
-        <v>0.8807423718119111</v>
+        <v>0.7288477421072059</v>
       </c>
       <c r="F71">
-        <v>0.5069473236556038</v>
+        <v>0.3576238240448292</v>
       </c>
       <c r="G71">
-        <v>2.207746878813811</v>
+        <v>2.052786962979538</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4838,32 +4838,32 @@
         </is>
       </c>
       <c r="O71">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B72">
-        <v>0.7702552089103839</v>
+        <v>0.7660934742023177</v>
       </c>
       <c r="C72">
-        <v>0.2950397647693634</v>
+        <v>0.3011632710259984</v>
       </c>
       <c r="D72">
-        <v>-0.8847396523287496</v>
+        <v>-0.8847396523287394</v>
       </c>
       <c r="E72">
-        <v>0.3762970641886345</v>
+        <v>0.37629706418864</v>
       </c>
       <c r="F72">
-        <v>0.4320125276968111</v>
+        <v>0.4245522255639295</v>
       </c>
       <c r="G72">
-        <v>1.373323801549467</v>
+        <v>1.382395794618208</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4907,26 +4907,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B73">
-        <v>0.8054399254614986</v>
+        <v>0.545745006495251</v>
       </c>
       <c r="C73">
-        <v>0.2465051267053266</v>
+        <v>0.6899600491732306</v>
       </c>
       <c r="D73">
-        <v>-0.8777369561066561</v>
+        <v>-0.8777369561066514</v>
       </c>
       <c r="E73">
-        <v>0.3800864841615086</v>
+        <v>0.3800864841615112</v>
       </c>
       <c r="F73">
-        <v>0.4968297683712933</v>
+        <v>0.141154494814777</v>
       </c>
       <c r="G73">
-        <v>1.305745981473899</v>
+        <v>2.11001153385391</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.4067431345286706</v>
+        <v>0.3712846622194231</v>
       </c>
       <c r="C74">
-        <v>0.4464452055113468</v>
+        <v>0.4704787244622275</v>
       </c>
       <c r="D74">
-        <v>-2.014969364141471</v>
+        <v>-2.105910799916576</v>
       </c>
       <c r="E74">
-        <v>0.04390785916277757</v>
+        <v>0.03521210137024816</v>
       </c>
       <c r="F74">
-        <v>0.1695529628552467</v>
+        <v>0.1476504559997034</v>
       </c>
       <c r="G74">
-        <v>0.9757421793180351</v>
+        <v>0.9336395168306694</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="O74">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="75">
@@ -5037,22 +5037,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>1.862666791195298</v>
+        <v>1.3277283844649</v>
       </c>
       <c r="C75">
-        <v>0.4274937593092781</v>
+        <v>0.4272250489831837</v>
       </c>
       <c r="D75">
-        <v>1.455013566950406</v>
+        <v>0.6635132959535979</v>
       </c>
       <c r="E75">
-        <v>0.145665505616932</v>
+        <v>0.5070018668777401</v>
       </c>
       <c r="F75">
-        <v>0.8058455724572799</v>
+        <v>0.5747177611094543</v>
       </c>
       <c r="G75">
-        <v>4.305449696077741</v>
+        <v>3.067353720738828</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="O75">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="76">
@@ -5100,22 +5100,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.3476628606731872</v>
+        <v>0.3506224031102982</v>
       </c>
       <c r="C76">
-        <v>0.4738485656111552</v>
+        <v>0.4671020551755031</v>
       </c>
       <c r="D76">
-        <v>-2.229661830031012</v>
+        <v>-2.243718257240095</v>
       </c>
       <c r="E76">
-        <v>0.02576990171825548</v>
+        <v>0.02485053466533218</v>
       </c>
       <c r="F76">
-        <v>0.1373465228582974</v>
+        <v>0.1403594545377964</v>
       </c>
       <c r="G76">
-        <v>0.8800329427790968</v>
+        <v>0.8758659683287376</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="O76">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="77">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.398654971023212</v>
+        <v>1.138196777703275</v>
       </c>
       <c r="C77">
-        <v>0.4162847858996969</v>
+        <v>0.4366260301815325</v>
       </c>
       <c r="D77">
-        <v>0.8059651738436981</v>
+        <v>0.2964670614871807</v>
       </c>
       <c r="E77">
-        <v>0.4202629300862729</v>
+        <v>0.7668734180247205</v>
       </c>
       <c r="F77">
-        <v>0.6185407848081024</v>
+        <v>0.4836827522530624</v>
       </c>
       <c r="G77">
-        <v>3.162662472733872</v>
+        <v>2.678391773821861</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
         </is>
       </c>
       <c r="O77">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B78">
-        <v>0.3640842171721629</v>
+        <v>0.1746976298491037</v>
       </c>
       <c r="C78">
-        <v>0.5474691976366015</v>
+        <v>0.7995505114582948</v>
       </c>
       <c r="D78">
-        <v>-1.845528618980717</v>
+        <v>-2.182099321941645</v>
       </c>
       <c r="E78">
-        <v>0.06496067931807198</v>
+        <v>0.02910220324723643</v>
       </c>
       <c r="F78">
-        <v>0.1245074180325557</v>
+        <v>0.0364509107269253</v>
       </c>
       <c r="G78">
-        <v>1.064653972337665</v>
+        <v>0.8372702153735407</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5279,32 +5279,32 @@
         </is>
       </c>
       <c r="O78">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B79">
-        <v>1.71674931954883</v>
+        <v>1.337435973381941</v>
       </c>
       <c r="C79">
-        <v>0.4879787393023182</v>
+        <v>0.7383674548310727</v>
       </c>
       <c r="D79">
-        <v>1.107492045516503</v>
+        <v>0.3937799890436393</v>
       </c>
       <c r="E79">
-        <v>0.2680812495407301</v>
+        <v>0.6937434796614685</v>
       </c>
       <c r="F79">
-        <v>0.6596880665690149</v>
+        <v>0.3146106958916202</v>
       </c>
       <c r="G79">
-        <v>4.467608822302441</v>
+        <v>5.685550447758135</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5342,32 +5342,32 @@
         </is>
       </c>
       <c r="O79">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B80">
-        <v>0.3082967262992932</v>
+        <v>0.1444728371834296</v>
       </c>
       <c r="C80">
-        <v>0.5505564453243098</v>
+        <v>0.8466159332230491</v>
       </c>
       <c r="D80">
-        <v>-2.137278698115902</v>
+        <v>-2.285172876092521</v>
       </c>
       <c r="E80">
-        <v>0.03257533039007404</v>
+        <v>0.02230269297329646</v>
       </c>
       <c r="F80">
-        <v>0.1047935172831068</v>
+        <v>0.02748814371468434</v>
       </c>
       <c r="G80">
-        <v>0.9069919009406443</v>
+        <v>0.7593237615634117</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5405,32 +5405,32 @@
         </is>
       </c>
       <c r="O80">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B81">
-        <v>1.237547457549414</v>
+        <v>1.060202440509069</v>
       </c>
       <c r="C81">
-        <v>0.5113879942565032</v>
+        <v>0.7553648396722332</v>
       </c>
       <c r="D81">
-        <v>0.4167707624230231</v>
+        <v>0.07739289470635867</v>
       </c>
       <c r="E81">
-        <v>0.6768460899706716</v>
+        <v>0.9383109930337662</v>
       </c>
       <c r="F81">
-        <v>0.4542214218044088</v>
+        <v>0.2412243153156218</v>
       </c>
       <c r="G81">
-        <v>3.371755791708352</v>
+        <v>4.659684548759889</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5468,32 +5468,32 @@
         </is>
       </c>
       <c r="O81">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B82">
-        <v>0.3876646528472182</v>
+        <v>0.2147971885926073</v>
       </c>
       <c r="C82">
-        <v>0.4646643065325172</v>
+        <v>0.6704791449250075</v>
       </c>
       <c r="D82">
-        <v>-2.039353134170396</v>
+        <v>-2.293972924532807</v>
       </c>
       <c r="E82">
-        <v>0.04141479620624581</v>
+        <v>0.02179205401165507</v>
       </c>
       <c r="F82">
-        <v>0.155931274704289</v>
+        <v>0.05771858955494173</v>
       </c>
       <c r="G82">
-        <v>0.9637828161935791</v>
+        <v>0.7993582757834019</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5531,32 +5531,32 @@
         </is>
       </c>
       <c r="O82">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B83">
-        <v>1.708318931319312</v>
+        <v>1.362529649665635</v>
       </c>
       <c r="C83">
-        <v>0.4157782827447591</v>
+        <v>0.6160696972333136</v>
       </c>
       <c r="D83">
-        <v>1.287969641748548</v>
+        <v>0.5021233959894355</v>
       </c>
       <c r="E83">
-        <v>0.1977565311186528</v>
+        <v>0.6155807237860056</v>
       </c>
       <c r="F83">
-        <v>0.7562368532956598</v>
+        <v>0.4073300819773827</v>
       </c>
       <c r="G83">
-        <v>3.859047014683097</v>
+        <v>4.557696886038094</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5594,32 +5594,32 @@
         </is>
       </c>
       <c r="O83">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B84">
-        <v>0.3302005130295403</v>
+        <v>0.1824378189024235</v>
       </c>
       <c r="C84">
-        <v>0.4745255317903914</v>
+        <v>0.7071770260135042</v>
       </c>
       <c r="D84">
-        <v>-2.335080242412396</v>
+        <v>-2.405827423369477</v>
       </c>
       <c r="E84">
-        <v>0.01953922925398219</v>
+        <v>0.01613588519610834</v>
       </c>
       <c r="F84">
-        <v>0.1302749390741743</v>
+        <v>0.04562098896496276</v>
       </c>
       <c r="G84">
-        <v>0.8369405472751139</v>
+        <v>0.7295667744387454</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5657,32 +5657,32 @@
         </is>
       </c>
       <c r="O84">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B85">
-        <v>1.282667357613483</v>
+        <v>1.115951587098342</v>
       </c>
       <c r="C85">
-        <v>0.4323566968903926</v>
+        <v>0.6448539034618052</v>
       </c>
       <c r="D85">
-        <v>0.5757787137463146</v>
+        <v>0.1701276547958322</v>
       </c>
       <c r="E85">
-        <v>0.5647647631087147</v>
+        <v>0.8649097451534535</v>
       </c>
       <c r="F85">
-        <v>0.5496564833757519</v>
+        <v>0.3153150618112398</v>
       </c>
       <c r="G85">
-        <v>2.993206848362509</v>
+        <v>3.949535228649568</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="O85">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="86">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.415580478163049</v>
+        <v>0.4499379477225906</v>
       </c>
       <c r="C86">
-        <v>0.3531847915571114</v>
+        <v>0.3909074635372705</v>
       </c>
       <c r="D86">
-        <v>-2.486174417782127</v>
+        <v>-2.043055388221487</v>
       </c>
       <c r="E86">
-        <v>0.0129124662621201</v>
+        <v>0.04104695543637375</v>
       </c>
       <c r="F86">
-        <v>0.2079810176261309</v>
+        <v>0.2091277124061438</v>
       </c>
       <c r="G86">
-        <v>0.8303985421433452</v>
+        <v>0.9680407941710418</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="O86">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="87">
@@ -5793,22 +5793,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.77866160974719</v>
+        <v>1.4294892993055</v>
       </c>
       <c r="C87">
-        <v>0.3764584068824282</v>
+        <v>0.3666013010739285</v>
       </c>
       <c r="D87">
-        <v>1.52968074644528</v>
+        <v>0.9746753382625306</v>
       </c>
       <c r="E87">
-        <v>0.1260957716505591</v>
+        <v>0.329721329829507</v>
       </c>
       <c r="F87">
-        <v>0.8504550308524208</v>
+        <v>0.6968339724656181</v>
       </c>
       <c r="G87">
-        <v>3.719934631720052</v>
+        <v>2.932462735131289</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O87">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="88">
@@ -5856,22 +5856,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.3612309780704227</v>
+        <v>0.4092655743952112</v>
       </c>
       <c r="C88">
-        <v>0.4266816423516342</v>
+        <v>0.4066879686335912</v>
       </c>
       <c r="D88">
-        <v>-2.386410840621874</v>
+        <v>-2.196748063416634</v>
       </c>
       <c r="E88">
-        <v>0.01701373230085267</v>
+        <v>0.02803844416593693</v>
       </c>
       <c r="F88">
-        <v>0.1565283165924717</v>
+        <v>0.1844300944851994</v>
       </c>
       <c r="G88">
-        <v>0.8336371485898293</v>
+        <v>0.9081940279463664</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="O88">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="89">
@@ -5919,22 +5919,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.267167053625939</v>
+        <v>1.153933310048906</v>
       </c>
       <c r="C89">
-        <v>0.3372784066716422</v>
+        <v>0.3779912858312749</v>
       </c>
       <c r="D89">
-        <v>0.7020424009009847</v>
+        <v>0.3787822141160395</v>
       </c>
       <c r="E89">
-        <v>0.4826527212434683</v>
+        <v>0.7048495960309584</v>
       </c>
       <c r="F89">
-        <v>0.6542473503741414</v>
+        <v>0.5500902460241818</v>
       </c>
       <c r="G89">
-        <v>2.45428940732705</v>
+        <v>2.420624785959011</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5972,32 +5972,32 @@
         </is>
       </c>
       <c r="O89">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B90">
-        <v>0.3917607731928112</v>
+        <v>0.2457417039743205</v>
       </c>
       <c r="C90">
-        <v>0.4336113350667745</v>
+        <v>0.6548661824009021</v>
       </c>
       <c r="D90">
-        <v>-2.161160980274469</v>
+        <v>-2.143146670618587</v>
       </c>
       <c r="E90">
-        <v>0.03068290639245949</v>
+        <v>0.03210132292510331</v>
       </c>
       <c r="F90">
-        <v>0.1674674126529521</v>
+        <v>0.06808567701973084</v>
       </c>
       <c r="G90">
-        <v>0.9164559300302999</v>
+        <v>0.8869557844699434</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6035,32 +6035,32 @@
         </is>
       </c>
       <c r="O90">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B91">
-        <v>1.779672053772581</v>
+        <v>1.718632937506967</v>
       </c>
       <c r="C91">
-        <v>0.4208130803027891</v>
+        <v>0.6068530432502138</v>
       </c>
       <c r="D91">
-        <v>1.369798456505806</v>
+        <v>0.8923563571931858</v>
       </c>
       <c r="E91">
-        <v>0.1707498240244337</v>
+        <v>0.3722019557247372</v>
       </c>
       <c r="F91">
-        <v>0.780087353626232</v>
+        <v>0.5231531972422997</v>
       </c>
       <c r="G91">
-        <v>4.06009994170044</v>
+        <v>5.645954549171594</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6098,32 +6098,32 @@
         </is>
       </c>
       <c r="O91">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B92">
-        <v>0.3232296748066463</v>
+        <v>0.1972043662289036</v>
       </c>
       <c r="C92">
-        <v>0.4804434890154699</v>
+        <v>0.688115192349302</v>
       </c>
       <c r="D92">
-        <v>-2.350728372341421</v>
+        <v>-2.359364702290109</v>
       </c>
       <c r="E92">
-        <v>0.01873670598769913</v>
+        <v>0.01830625491010182</v>
       </c>
       <c r="F92">
-        <v>0.1260541029105449</v>
+        <v>0.05119078773593552</v>
       </c>
       <c r="G92">
-        <v>0.8288300044446264</v>
+        <v>0.759698449266945</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6161,32 +6161,32 @@
         </is>
       </c>
       <c r="O92">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B93">
-        <v>1.249687213808787</v>
+        <v>1.285972224809249</v>
       </c>
       <c r="C93">
-        <v>0.4072232431484881</v>
+        <v>0.6266162444729609</v>
       </c>
       <c r="D93">
-        <v>0.5473491378474096</v>
+        <v>0.401386063119342</v>
       </c>
       <c r="E93">
-        <v>0.5841388913005818</v>
+        <v>0.6881359087389085</v>
       </c>
       <c r="F93">
-        <v>0.562564435654288</v>
+        <v>0.3765779390114435</v>
       </c>
       <c r="G93">
-        <v>2.776069785749643</v>
+        <v>4.39145364521897</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6224,32 +6224,32 @@
         </is>
       </c>
       <c r="O93">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B94">
-        <v>0.383382136441546</v>
+        <v>0.3738211199679969</v>
       </c>
       <c r="C94">
-        <v>0.3577861664095956</v>
+        <v>0.4091055291757064</v>
       </c>
       <c r="D94">
-        <v>-2.679597849075964</v>
+        <v>-2.405193317290072</v>
       </c>
       <c r="E94">
-        <v>0.007371065642614373</v>
+        <v>0.01616391266089837</v>
       </c>
       <c r="F94">
-        <v>0.1901444861745379</v>
+        <v>0.1676612024403737</v>
       </c>
       <c r="G94">
-        <v>0.7730009189304928</v>
+        <v>0.8334798253867041</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6287,32 +6287,32 @@
         </is>
       </c>
       <c r="O94">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B95">
-        <v>1.607377900285555</v>
+        <v>1.393840405247607</v>
       </c>
       <c r="C95">
-        <v>0.3553144662892379</v>
+        <v>0.3728864602691571</v>
       </c>
       <c r="D95">
-        <v>1.335730072926407</v>
+        <v>0.8905199149216135</v>
       </c>
       <c r="E95">
-        <v>0.1816375161636689</v>
+        <v>0.3731867798518935</v>
       </c>
       <c r="F95">
-        <v>0.8010760928221513</v>
+        <v>0.6711375210701196</v>
       </c>
       <c r="G95">
-        <v>3.22524131911649</v>
+        <v>2.894773447032228</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6350,32 +6350,32 @@
         </is>
       </c>
       <c r="O95">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B96">
-        <v>0.3387838362360635</v>
+        <v>0.3348898977341579</v>
       </c>
       <c r="C96">
-        <v>0.4131093260697636</v>
+        <v>0.4244320661618659</v>
       </c>
       <c r="D96">
-        <v>-2.620112783476483</v>
+        <v>-2.577452440272675</v>
       </c>
       <c r="E96">
-        <v>0.008790069088255002</v>
+        <v>0.009953157730940311</v>
       </c>
       <c r="F96">
-        <v>0.15075904774256</v>
+        <v>0.1457554548732887</v>
       </c>
       <c r="G96">
-        <v>0.7613107764571168</v>
+        <v>0.7694480024908332</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6413,32 +6413,32 @@
         </is>
       </c>
       <c r="O96">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B97">
-        <v>1.13016940408853</v>
+        <v>1.132863571125341</v>
       </c>
       <c r="C97">
-        <v>0.3334145101511966</v>
+        <v>0.3990596194722572</v>
       </c>
       <c r="D97">
-        <v>0.3670132309334764</v>
+        <v>0.3126063246536109</v>
       </c>
       <c r="E97">
-        <v>0.7136091487998166</v>
+        <v>0.7545797724218383</v>
       </c>
       <c r="F97">
-        <v>0.5879502783967403</v>
+        <v>0.5182000466199354</v>
       </c>
       <c r="G97">
-        <v>2.172433501385182</v>
+        <v>2.476610874803978</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="O97">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="98">
@@ -6486,22 +6486,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.7888261627530694</v>
+        <v>0.3985930444756969</v>
       </c>
       <c r="C98">
-        <v>0.9018835594654887</v>
+        <v>0.9369965022116687</v>
       </c>
       <c r="D98">
-        <v>-0.2630154480185144</v>
+        <v>-0.9816624918769047</v>
       </c>
       <c r="E98">
-        <v>0.7925386723959607</v>
+        <v>0.326266149632214</v>
       </c>
       <c r="F98">
-        <v>0.1346779907826222</v>
+        <v>0.0635267806662794</v>
       </c>
       <c r="G98">
-        <v>4.620255406453702</v>
+        <v>2.500936037338627</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="O98">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="99">
@@ -6549,22 +6549,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>1.999558045502126</v>
+        <v>1.263624341855124</v>
       </c>
       <c r="C99">
-        <v>0.6767860701345714</v>
+        <v>0.7827354593031739</v>
       </c>
       <c r="D99">
-        <v>1.023848169265893</v>
+        <v>0.298931204498508</v>
       </c>
       <c r="E99">
-        <v>0.3059069945527105</v>
+        <v>0.7649925373443067</v>
       </c>
       <c r="F99">
-        <v>0.5307043758189528</v>
+        <v>0.2724911190632648</v>
       </c>
       <c r="G99">
-        <v>7.533822141870301</v>
+        <v>5.859811075010028</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="O99">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="100">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.7510276610552328</v>
+        <v>0.6263646714072991</v>
       </c>
       <c r="C100">
-        <v>0.8309053321232974</v>
+        <v>0.9769624467437978</v>
       </c>
       <c r="D100">
-        <v>-0.3445793215304118</v>
+        <v>-0.4788541636057059</v>
       </c>
       <c r="E100">
-        <v>0.7304106537679904</v>
+        <v>0.6320423811769601</v>
       </c>
       <c r="F100">
-        <v>0.1473628566531797</v>
+        <v>0.09230714358550075</v>
       </c>
       <c r="G100">
-        <v>3.82757609672005</v>
+        <v>4.250296199706041</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="O100">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="101">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>3.660487146963901</v>
+        <v>1.815162825189424</v>
       </c>
       <c r="C101">
-        <v>0.8062940904585046</v>
+        <v>0.8245876794821829</v>
       </c>
       <c r="D101">
-        <v>1.609333683794823</v>
+        <v>0.7229979168686886</v>
       </c>
       <c r="E101">
-        <v>0.1075433975163546</v>
+        <v>0.4696811640194901</v>
       </c>
       <c r="F101">
-        <v>0.7537374814577663</v>
+        <v>0.3605996353880003</v>
       </c>
       <c r="G101">
-        <v>17.77696675926645</v>
+        <v>9.137047735515521</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6728,32 +6728,32 @@
         </is>
       </c>
       <c r="O101">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B102">
-        <v>0.5708687919299577</v>
+        <v>0.1924031638845731</v>
       </c>
       <c r="C102">
-        <v>1.000342115009842</v>
+        <v>1.508401883488374</v>
       </c>
       <c r="D102">
-        <v>-0.5604041595189526</v>
+        <v>-1.092654626476358</v>
       </c>
       <c r="E102">
-        <v>0.5752037950959907</v>
+        <v>0.2745454685773949</v>
       </c>
       <c r="F102">
-        <v>0.08036067014122661</v>
+        <v>0.01000594700323432</v>
       </c>
       <c r="G102">
-        <v>4.055356644324208</v>
+        <v>3.699697535958155</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6791,32 +6791,32 @@
         </is>
       </c>
       <c r="O102">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B103">
-        <v>1.820219284585444</v>
+        <v>1.888851132325813</v>
       </c>
       <c r="C103">
-        <v>0.7596487525534711</v>
+        <v>1.310648349768326</v>
       </c>
       <c r="D103">
-        <v>0.7884656926684581</v>
+        <v>0.4852321966177636</v>
       </c>
       <c r="E103">
-        <v>0.4304243583249907</v>
+        <v>0.6275116457284027</v>
       </c>
       <c r="F103">
-        <v>0.4106856429924806</v>
+        <v>0.144734422602643</v>
       </c>
       <c r="G103">
-        <v>8.067480079982753</v>
+        <v>24.6503805793561</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6854,32 +6854,32 @@
         </is>
       </c>
       <c r="O103">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B104">
-        <v>0.5929969801926009</v>
+        <v>0.400729010089964</v>
       </c>
       <c r="C104">
-        <v>0.9341950344323249</v>
+        <v>1.61756015638744</v>
       </c>
       <c r="D104">
-        <v>-0.5593756690634372</v>
+        <v>-0.5653390149492303</v>
       </c>
       <c r="E104">
-        <v>0.5759053629964358</v>
+        <v>0.5718431964721644</v>
       </c>
       <c r="F104">
-        <v>0.09503076530951857</v>
+        <v>0.01682600765707618</v>
       </c>
       <c r="G104">
-        <v>3.700332385751314</v>
+        <v>9.543781436480508</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6917,32 +6917,32 @@
         </is>
       </c>
       <c r="O104">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B105">
-        <v>2.927807348039936</v>
+        <v>3.39215249607704</v>
       </c>
       <c r="C105">
-        <v>0.8863964277680816</v>
+        <v>1.371157135418231</v>
       </c>
       <c r="D105">
-        <v>1.211933807320133</v>
+        <v>0.8908276396172534</v>
       </c>
       <c r="E105">
-        <v>0.225537719683223</v>
+        <v>0.3730216446909655</v>
       </c>
       <c r="F105">
-        <v>0.5152766815008434</v>
+        <v>0.2308576647981559</v>
       </c>
       <c r="G105">
-        <v>16.63583114661596</v>
+        <v>49.84325977091669</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6980,32 +6980,32 @@
         </is>
       </c>
       <c r="O105">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B106">
-        <v>0.6330141400153678</v>
+        <v>0.2289994834722243</v>
       </c>
       <c r="C106">
-        <v>0.8949020674333539</v>
+        <v>1.319458821851675</v>
       </c>
       <c r="D106">
-        <v>-0.5109637530528541</v>
+        <v>-1.117151597760093</v>
       </c>
       <c r="E106">
-        <v>0.6093764380702004</v>
+        <v>0.2639295119305226</v>
       </c>
       <c r="F106">
-        <v>0.1095648857987571</v>
+        <v>0.01724682343904771</v>
       </c>
       <c r="G106">
-        <v>3.657256597660245</v>
+        <v>3.040604179423378</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7043,32 +7043,32 @@
         </is>
       </c>
       <c r="O106">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B107">
-        <v>1.863464236701189</v>
+        <v>1.617559017528944</v>
       </c>
       <c r="C107">
-        <v>0.6610683417114834</v>
+        <v>1.133917931396458</v>
       </c>
       <c r="D107">
-        <v>0.9415626328051322</v>
+        <v>0.4241208471016576</v>
       </c>
       <c r="E107">
-        <v>0.3464166084801188</v>
+        <v>0.6714776825706842</v>
       </c>
       <c r="F107">
-        <v>0.5100569500220444</v>
+        <v>0.1752537994110364</v>
       </c>
       <c r="G107">
-        <v>6.808061259265783</v>
+        <v>14.92976006216293</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7106,32 +7106,32 @@
         </is>
       </c>
       <c r="O107">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B108">
-        <v>0.6262275985397356</v>
+        <v>0.4447357633127028</v>
       </c>
       <c r="C108">
-        <v>0.8277570365646868</v>
+        <v>1.426963410871557</v>
       </c>
       <c r="D108">
-        <v>-0.5654333063239504</v>
+        <v>-0.5678316327626203</v>
       </c>
       <c r="E108">
-        <v>0.571779075748687</v>
+        <v>0.570149298279115</v>
       </c>
       <c r="F108">
-        <v>0.1236357696165374</v>
+        <v>0.02713117465293285</v>
       </c>
       <c r="G108">
-        <v>3.171905722665469</v>
+        <v>7.290134013712949</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7169,32 +7169,32 @@
         </is>
       </c>
       <c r="O108">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B109">
-        <v>3.232262315311896</v>
+        <v>2.885110812241928</v>
       </c>
       <c r="C109">
-        <v>0.7814240259792623</v>
+        <v>1.207794301393623</v>
       </c>
       <c r="D109">
-        <v>1.501338914952101</v>
+        <v>0.8772713265736307</v>
       </c>
       <c r="E109">
-        <v>0.1332679245953299</v>
+        <v>0.3803392825305528</v>
       </c>
       <c r="F109">
-        <v>0.6988070246732507</v>
+        <v>0.2704494640260046</v>
       </c>
       <c r="G109">
-        <v>14.95050751653575</v>
+        <v>30.77789201355159</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="O109">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="110">
@@ -7242,22 +7242,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.3584561919059169</v>
+        <v>0.3727475883603534</v>
       </c>
       <c r="C110">
-        <v>0.4692162172304289</v>
+        <v>0.5344254157175076</v>
       </c>
       <c r="D110">
-        <v>-2.186516124218491</v>
+        <v>-1.846569729269889</v>
       </c>
       <c r="E110">
-        <v>0.02877786632963523</v>
+        <v>0.06480952474319911</v>
       </c>
       <c r="F110">
-        <v>0.1429020695775852</v>
+        <v>0.1307708972968826</v>
       </c>
       <c r="G110">
-        <v>0.8991531186042798</v>
+        <v>1.062474659885748</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="O110">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="111">
@@ -7305,22 +7305,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>1.579167992882292</v>
+        <v>1.331924171465124</v>
       </c>
       <c r="C111">
-        <v>0.4932630805726346</v>
+        <v>0.4931845499806951</v>
       </c>
       <c r="D111">
-        <v>0.9262767467404729</v>
+        <v>0.5811711704664133</v>
       </c>
       <c r="E111">
-        <v>0.3543021771074557</v>
+        <v>0.5611250957766776</v>
       </c>
       <c r="F111">
-        <v>0.6005677919872922</v>
+        <v>0.5066173401453432</v>
       </c>
       <c r="G111">
-        <v>4.152356458364079</v>
+        <v>3.50170011556278</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="O111">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="112">
@@ -7368,22 +7368,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.463142107509019</v>
+        <v>0.5798504732929349</v>
       </c>
       <c r="C112">
-        <v>0.5338326985932622</v>
+        <v>0.5197260942952298</v>
       </c>
       <c r="D112">
-        <v>-1.441877476504603</v>
+        <v>-1.048600444211645</v>
       </c>
       <c r="E112">
-        <v>0.149336941245415</v>
+        <v>0.2943620513317162</v>
       </c>
       <c r="F112">
-        <v>0.1626728407095182</v>
+        <v>0.2093747773114075</v>
       </c>
       <c r="G112">
-        <v>1.318601253978993</v>
+        <v>1.605859959330077</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="O112">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="113">
@@ -7431,22 +7431,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>1.485675247819319</v>
+        <v>1.30516947524592</v>
       </c>
       <c r="C113">
-        <v>0.4345740761506714</v>
+        <v>0.5017939715278245</v>
       </c>
       <c r="D113">
-        <v>0.9109364846312804</v>
+        <v>0.530761454986602</v>
       </c>
       <c r="E113">
-        <v>0.3623288406405334</v>
+        <v>0.5955840936276431</v>
       </c>
       <c r="F113">
-        <v>0.6338898000367906</v>
+        <v>0.4881340523454405</v>
       </c>
       <c r="G113">
-        <v>3.482042055030525</v>
+        <v>3.489753175236805</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7484,32 +7484,32 @@
         </is>
       </c>
       <c r="O113">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B114">
-        <v>0.3864397330287969</v>
+        <v>0.1914224563859067</v>
       </c>
       <c r="C114">
-        <v>0.5987661152535588</v>
+        <v>0.9424125599543023</v>
       </c>
       <c r="D114">
-        <v>-1.587897726607638</v>
+        <v>-1.754298011409796</v>
       </c>
       <c r="E114">
-        <v>0.1123094676641609</v>
+        <v>0.07937945635380822</v>
       </c>
       <c r="F114">
-        <v>0.1195118948296504</v>
+        <v>0.03018629830860673</v>
       </c>
       <c r="G114">
-        <v>1.249546477998926</v>
+        <v>1.213880431254031</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7547,32 +7547,32 @@
         </is>
       </c>
       <c r="O114">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B115">
-        <v>1.633280874726118</v>
+        <v>1.907249376651286</v>
       </c>
       <c r="C115">
-        <v>0.5878705221083893</v>
+        <v>0.864509143634129</v>
       </c>
       <c r="D115">
-        <v>0.8345218546740091</v>
+        <v>0.7468539713100467</v>
       </c>
       <c r="E115">
-        <v>0.4039869772684356</v>
+        <v>0.4551517127641684</v>
       </c>
       <c r="F115">
-        <v>0.516017678985786</v>
+        <v>0.3503773022606272</v>
       </c>
       <c r="G115">
-        <v>5.169602756613293</v>
+        <v>10.38195157410882</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7610,32 +7610,32 @@
         </is>
       </c>
       <c r="O115">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B116">
-        <v>0.3898274727191769</v>
+        <v>0.2862317110407399</v>
       </c>
       <c r="C116">
-        <v>0.665336454263095</v>
+        <v>0.9474384107083345</v>
       </c>
       <c r="D116">
-        <v>-1.415901698070674</v>
+        <v>-1.320353495886158</v>
       </c>
       <c r="E116">
-        <v>0.1568042877203588</v>
+        <v>0.1867170224057649</v>
       </c>
       <c r="F116">
-        <v>0.1058125122480196</v>
+        <v>0.04469477027582344</v>
       </c>
       <c r="G116">
-        <v>1.436176641666163</v>
+        <v>1.833068878074688</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7673,32 +7673,32 @@
         </is>
       </c>
       <c r="O116">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B117">
-        <v>1.725640630163075</v>
+        <v>2.367357870246097</v>
       </c>
       <c r="C117">
-        <v>0.5622427795399995</v>
+        <v>0.8836585226026962</v>
       </c>
       <c r="D117">
-        <v>0.9703963860415893</v>
+        <v>0.9752347638212008</v>
       </c>
       <c r="E117">
-        <v>0.3318489493864664</v>
+        <v>0.3294438216412195</v>
       </c>
       <c r="F117">
-        <v>0.5732821717624544</v>
+        <v>0.4188826925343073</v>
       </c>
       <c r="G117">
-        <v>5.194362795749928</v>
+        <v>13.37936225511902</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7736,32 +7736,32 @@
         </is>
       </c>
       <c r="O117">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B118">
-        <v>0.3137662684825243</v>
+        <v>0.2774649018733938</v>
       </c>
       <c r="C118">
-        <v>0.4921102527638992</v>
+        <v>0.5847659782925985</v>
       </c>
       <c r="D118">
-        <v>-2.355380591306997</v>
+        <v>-2.192434035361919</v>
       </c>
       <c r="E118">
-        <v>0.01850374299225372</v>
+        <v>0.02834818130514232</v>
       </c>
       <c r="F118">
-        <v>0.1195972644781544</v>
+        <v>0.08819710934539285</v>
       </c>
       <c r="G118">
-        <v>0.8231732696146259</v>
+        <v>0.8728945012258913</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7799,32 +7799,32 @@
         </is>
       </c>
       <c r="O118">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B119">
-        <v>1.469254118625875</v>
+        <v>1.384429916102129</v>
       </c>
       <c r="C119">
-        <v>0.4856374357577146</v>
+        <v>0.5250683772732839</v>
       </c>
       <c r="D119">
-        <v>0.7922677318376475</v>
+        <v>0.6195163450330868</v>
       </c>
       <c r="E119">
-        <v>0.4282045825297516</v>
+        <v>0.5355762575877469</v>
       </c>
       <c r="F119">
-        <v>0.5671808799296901</v>
+        <v>0.4946886684587355</v>
       </c>
       <c r="G119">
-        <v>3.80603038904749</v>
+        <v>3.874449355329074</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7862,32 +7862,32 @@
         </is>
       </c>
       <c r="O119">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B120">
-        <v>0.4073823643625936</v>
+        <v>0.437592392284616</v>
       </c>
       <c r="C120">
-        <v>0.5411840405718479</v>
+        <v>0.565471090707785</v>
       </c>
       <c r="D120">
-        <v>-1.659330277807535</v>
+        <v>-1.461555553761415</v>
       </c>
       <c r="E120">
-        <v>0.0970492572897193</v>
+        <v>0.1438630415769355</v>
       </c>
       <c r="F120">
-        <v>0.1410410504665525</v>
+        <v>0.1444574345804798</v>
       </c>
       <c r="G120">
-        <v>1.176681471420365</v>
+        <v>1.325560725493103</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7925,32 +7925,32 @@
         </is>
       </c>
       <c r="O120">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B121">
-        <v>1.376428604391402</v>
+        <v>1.458385258394906</v>
       </c>
       <c r="C121">
-        <v>0.4469476320450034</v>
+        <v>0.5557151203158767</v>
       </c>
       <c r="D121">
-        <v>0.7148313445520905</v>
+        <v>0.6789986856028419</v>
       </c>
       <c r="E121">
-        <v>0.4747132643481739</v>
+        <v>0.4971386947726804</v>
       </c>
       <c r="F121">
-        <v>0.5732065906935285</v>
+        <v>0.4907346204334925</v>
       </c>
       <c r="G121">
-        <v>3.305188275477818</v>
+        <v>4.334089084696699</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="O121">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="122">
@@ -7998,22 +7998,22 @@
         </is>
       </c>
       <c r="B122">
-        <v>1.471997437560516</v>
+        <v>1.001984370383448</v>
       </c>
       <c r="C122">
-        <v>0.4160385430770006</v>
+        <v>0.4107893118016683</v>
       </c>
       <c r="D122">
-        <v>0.9292895717258602</v>
+        <v>0.004825841530806426</v>
       </c>
       <c r="E122">
-        <v>0.3527390381193971</v>
+        <v>0.9961495504950512</v>
       </c>
       <c r="F122">
-        <v>0.6512899911172271</v>
+        <v>0.447915870956993</v>
       </c>
       <c r="G122">
-        <v>3.32689966948183</v>
+        <v>2.241431357070873</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="O122">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="123">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.7651889331120676</v>
+        <v>0.8207193833754267</v>
       </c>
       <c r="C123">
-        <v>0.2587422116140381</v>
+        <v>0.2249699355827028</v>
       </c>
       <c r="D123">
-        <v>-1.034359653147411</v>
+        <v>-0.878224132538903</v>
       </c>
       <c r="E123">
-        <v>0.3009680589067847</v>
+        <v>0.3798220981848189</v>
       </c>
       <c r="F123">
-        <v>0.4608153215307755</v>
+        <v>0.5280802607294127</v>
       </c>
       <c r="G123">
-        <v>1.27060467827366</v>
+        <v>1.27552638554934</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="O123">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="124">
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.371555655265801</v>
+        <v>0.8656481337132996</v>
       </c>
       <c r="C124">
-        <v>0.4168259902524863</v>
+        <v>0.4181669750073262</v>
       </c>
       <c r="D124">
-        <v>0.7579796313370828</v>
+        <v>-0.3450219020611544</v>
       </c>
       <c r="E124">
-        <v>0.4484631765858253</v>
+        <v>0.7300779051355203</v>
       </c>
       <c r="F124">
-        <v>0.6059133328182771</v>
+        <v>0.3814143447928675</v>
       </c>
       <c r="G124">
-        <v>3.104676549601184</v>
+        <v>1.96465261894715</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8177,32 +8177,32 @@
         </is>
       </c>
       <c r="O124">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B125">
-        <v>1.902618078387676</v>
+        <v>1.503183655307805</v>
       </c>
       <c r="C125">
-        <v>0.4915189429370755</v>
+        <v>0.7470449871527196</v>
       </c>
       <c r="D125">
-        <v>1.308659377072377</v>
+        <v>0.5455967214856857</v>
       </c>
       <c r="E125">
-        <v>0.1906497579823861</v>
+        <v>0.5853431784803502</v>
       </c>
       <c r="F125">
-        <v>0.7260556950226414</v>
+        <v>0.3476371645050937</v>
       </c>
       <c r="G125">
-        <v>4.985782188644258</v>
+        <v>6.499768529643001</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8240,32 +8240,32 @@
         </is>
       </c>
       <c r="O125">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B126">
-        <v>0.7348489081230498</v>
+        <v>0.7609362092114333</v>
       </c>
       <c r="C126">
-        <v>0.2751208743762316</v>
+        <v>0.3636889723037983</v>
       </c>
       <c r="D126">
-        <v>-1.119836394745298</v>
+        <v>-0.7512071313448234</v>
       </c>
       <c r="E126">
-        <v>0.2627834869371273</v>
+        <v>0.4525280090694187</v>
       </c>
       <c r="F126">
-        <v>0.428563065996147</v>
+        <v>0.3730573801915464</v>
       </c>
       <c r="G126">
-        <v>1.260031394713079</v>
+        <v>1.552104167438709</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8303,32 +8303,32 @@
         </is>
       </c>
       <c r="O126">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B127">
-        <v>1.718626636047382</v>
+        <v>1.185955875647173</v>
       </c>
       <c r="C127">
-        <v>0.4827834535545751</v>
+        <v>0.7550120863847439</v>
       </c>
       <c r="D127">
-        <v>1.121673703767353</v>
+        <v>0.2258892256352766</v>
       </c>
       <c r="E127">
-        <v>0.2620012012244721</v>
+        <v>0.8212875779596518</v>
       </c>
       <c r="F127">
-        <v>0.6671684762819396</v>
+        <v>0.2700231989418979</v>
       </c>
       <c r="G127">
-        <v>4.427183866048466</v>
+        <v>5.208779632614806</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8366,32 +8366,32 @@
         </is>
       </c>
       <c r="O127">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B128">
-        <v>1.729872286597307</v>
+        <v>1.319286750240557</v>
       </c>
       <c r="C128">
-        <v>0.4207873174109729</v>
+        <v>0.6244851302181866</v>
       </c>
       <c r="D128">
-        <v>1.302433700665137</v>
+        <v>0.4437115255858177</v>
       </c>
       <c r="E128">
-        <v>0.192768168387826</v>
+        <v>0.6572511614945908</v>
       </c>
       <c r="F128">
-        <v>0.7582968068107661</v>
+        <v>0.3879506592705687</v>
       </c>
       <c r="G128">
-        <v>3.946288710515654</v>
+        <v>4.486440447434322</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8429,32 +8429,32 @@
         </is>
       </c>
       <c r="O128">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B129">
-        <v>0.7351200259060175</v>
+        <v>0.7495408841084947</v>
       </c>
       <c r="C129">
-        <v>0.2576114557769558</v>
+        <v>0.3385361542810397</v>
       </c>
       <c r="D129">
-        <v>-1.194517889823229</v>
+        <v>-0.8515912134381265</v>
       </c>
       <c r="E129">
-        <v>0.2322754469769731</v>
+        <v>0.3944410180455482</v>
       </c>
       <c r="F129">
-        <v>0.4436893303503868</v>
+        <v>0.3860404646653559</v>
       </c>
       <c r="G129">
-        <v>1.217972611740072</v>
+        <v>1.455317740945</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8492,32 +8492,32 @@
         </is>
       </c>
       <c r="O129">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B130">
-        <v>1.613421995961287</v>
+        <v>1.082428401318102</v>
       </c>
       <c r="C130">
-        <v>0.4181389993240815</v>
+        <v>0.6438509975535869</v>
       </c>
       <c r="D130">
-        <v>1.144015237751101</v>
+        <v>0.1230207564150241</v>
       </c>
       <c r="E130">
-        <v>0.2526173177027102</v>
+        <v>0.9020906615697579</v>
       </c>
       <c r="F130">
-        <v>0.7109309344661243</v>
+        <v>0.3064447717541008</v>
       </c>
       <c r="G130">
-        <v>3.661580064745011</v>
+        <v>3.823368358590318</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="O130">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="131">
@@ -8565,22 +8565,22 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.9124503887857419</v>
+        <v>0.8251737527830237</v>
       </c>
       <c r="C131">
-        <v>0.2817903671055506</v>
+        <v>0.265556606361664</v>
       </c>
       <c r="D131">
-        <v>-0.3251408641061568</v>
+        <v>-0.7236171150900874</v>
       </c>
       <c r="E131">
-        <v>0.7450744625913753</v>
+        <v>0.4693008310105578</v>
       </c>
       <c r="F131">
-        <v>0.5252292031812249</v>
+        <v>0.4903466496606114</v>
       </c>
       <c r="G131">
-        <v>1.585147411744323</v>
+        <v>1.388633373457951</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="O131">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="132">
@@ -8628,22 +8628,22 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.8473842512457328</v>
+        <v>0.8084983847998598</v>
       </c>
       <c r="C132">
-        <v>0.2439859694292486</v>
+        <v>0.2210031276213242</v>
       </c>
       <c r="D132">
-        <v>-0.6787317571726194</v>
+        <v>-0.9618714451183552</v>
       </c>
       <c r="E132">
-        <v>0.4973078404301464</v>
+        <v>0.3361141839111136</v>
       </c>
       <c r="F132">
-        <v>0.5252900259355303</v>
+        <v>0.5242771782705001</v>
       </c>
       <c r="G132">
-        <v>1.366978304947713</v>
+        <v>1.246801625774224</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="O132">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="133">
@@ -8691,22 +8691,22 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.7993534306381261</v>
+        <v>0.6690656754914149</v>
       </c>
       <c r="C133">
-        <v>0.2936849525230174</v>
+        <v>0.2818964486204191</v>
       </c>
       <c r="D133">
-        <v>-0.7625589526183192</v>
+        <v>-1.425605239071297</v>
       </c>
       <c r="E133">
-        <v>0.4457264723144892</v>
+        <v>0.1539823231328821</v>
       </c>
       <c r="F133">
-        <v>0.4495249054749058</v>
+        <v>0.3850508248943645</v>
       </c>
       <c r="G133">
-        <v>1.421424929499509</v>
+        <v>1.162570884619172</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8744,32 +8744,32 @@
         </is>
       </c>
       <c r="O133">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B134">
-        <v>1.355005236305717</v>
+        <v>1.080171046619103</v>
       </c>
       <c r="C134">
-        <v>0.4082000606274281</v>
+        <v>0.5787359330659391</v>
       </c>
       <c r="D134">
-        <v>0.7442559373692732</v>
+        <v>0.1332549107267507</v>
       </c>
       <c r="E134">
-        <v>0.45672165277635</v>
+        <v>0.8939917855314247</v>
       </c>
       <c r="F134">
-        <v>0.6088081420691169</v>
+        <v>0.347433437087925</v>
       </c>
       <c r="G134">
-        <v>3.015792765477616</v>
+        <v>3.35825330956541</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8807,32 +8807,32 @@
         </is>
       </c>
       <c r="O134">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B135">
-        <v>0.7562462051058959</v>
+        <v>0.7004299248349332</v>
       </c>
       <c r="C135">
-        <v>0.2633055653886318</v>
+        <v>0.3407875492675445</v>
       </c>
       <c r="D135">
-        <v>-1.061080069762663</v>
+        <v>-1.044817966204223</v>
       </c>
       <c r="E135">
-        <v>0.2886535144482261</v>
+        <v>0.296107109652203</v>
       </c>
       <c r="F135">
-        <v>0.451374587715335</v>
+        <v>0.3591582150697564</v>
       </c>
       <c r="G135">
-        <v>1.267037042629768</v>
+        <v>1.365977608249847</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8870,32 +8870,32 @@
         </is>
       </c>
       <c r="O135">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B136">
-        <v>1.183677501018037</v>
+        <v>0.8116670585297627</v>
       </c>
       <c r="C136">
-        <v>0.4094017026385683</v>
+        <v>0.5937971466416979</v>
       </c>
       <c r="D136">
-        <v>0.4118842627563276</v>
+        <v>-0.3514079690776531</v>
       </c>
       <c r="E136">
-        <v>0.6804242560899556</v>
+        <v>0.7252823046984237</v>
       </c>
       <c r="F136">
-        <v>0.5305789692156132</v>
+        <v>0.2534760162486207</v>
       </c>
       <c r="G136">
-        <v>2.640685944427132</v>
+        <v>2.599075934885189</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8933,32 +8933,32 @@
         </is>
       </c>
       <c r="O136">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B137">
-        <v>0.9841651524157731</v>
+        <v>0.8482521552617573</v>
       </c>
       <c r="C137">
-        <v>0.3141475024379378</v>
+        <v>0.3225831785751342</v>
       </c>
       <c r="D137">
-        <v>-0.05080912013718974</v>
+        <v>-0.5101857301263415</v>
       </c>
       <c r="E137">
-        <v>0.9594776234471323</v>
+        <v>0.6099213484484725</v>
       </c>
       <c r="F137">
-        <v>0.5316981441937729</v>
+        <v>0.4507561619682308</v>
       </c>
       <c r="G137">
-        <v>1.821674681032121</v>
+        <v>1.596277055347119</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8996,32 +8996,32 @@
         </is>
       </c>
       <c r="O137">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B138">
-        <v>0.8046373820498747</v>
+        <v>0.7653753967712859</v>
       </c>
       <c r="C138">
-        <v>0.2441223186036296</v>
+        <v>0.2360391095347392</v>
       </c>
       <c r="D138">
-        <v>-0.8903879062514845</v>
+        <v>-1.132815876614898</v>
       </c>
       <c r="E138">
-        <v>0.3732576339046897</v>
+        <v>0.2572915827396823</v>
       </c>
       <c r="F138">
-        <v>0.4986581378937797</v>
+        <v>0.4819007955799015</v>
       </c>
       <c r="G138">
-        <v>1.298367092386626</v>
+        <v>1.215601848670687</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9059,32 +9059,32 @@
         </is>
       </c>
       <c r="O138">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B139">
-        <v>0.8667241717320729</v>
+        <v>0.6826839948501656</v>
       </c>
       <c r="C139">
-        <v>0.3203046992068226</v>
+        <v>0.3459802881416553</v>
       </c>
       <c r="D139">
-        <v>-0.446557587814114</v>
+        <v>-1.103309095388135</v>
       </c>
       <c r="E139">
-        <v>0.6551945240214835</v>
+        <v>0.2698929581236661</v>
       </c>
       <c r="F139">
-        <v>0.4626334753251578</v>
+        <v>0.3465139841566408</v>
       </c>
       <c r="G139">
-        <v>1.623770932997588</v>
+        <v>1.344988826234213</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="O139">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="140">
@@ -9132,22 +9132,22 @@
         </is>
       </c>
       <c r="B140">
-        <v>2.10068654662874</v>
+        <v>1.641623025039714</v>
       </c>
       <c r="C140">
-        <v>0.650231130415586</v>
+        <v>0.7392169459565574</v>
       </c>
       <c r="D140">
-        <v>1.141539036730001</v>
+        <v>0.6705547060058411</v>
       </c>
       <c r="E140">
-        <v>0.2536456768511318</v>
+        <v>0.5025042451008793</v>
       </c>
       <c r="F140">
-        <v>0.5873317958019731</v>
+        <v>0.3855234765131919</v>
       </c>
       <c r="G140">
-        <v>7.513442995473115</v>
+        <v>6.990303627458409</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="O140">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="141">
@@ -9195,22 +9195,22 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.8881328724283865</v>
+        <v>1.401988339886638</v>
       </c>
       <c r="C141">
-        <v>0.5354191982006254</v>
+        <v>0.5313535732155847</v>
       </c>
       <c r="D141">
-        <v>-0.2215720251892885</v>
+        <v>0.6359070284626142</v>
       </c>
       <c r="E141">
-        <v>0.8246470618581373</v>
+        <v>0.5248370213463736</v>
       </c>
       <c r="F141">
-        <v>0.3109770196993221</v>
+        <v>0.4948293146566013</v>
       </c>
       <c r="G141">
-        <v>2.536457516541105</v>
+        <v>3.972220818287914</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="O141">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="142">
@@ -9258,22 +9258,22 @@
         </is>
       </c>
       <c r="B142">
-        <v>4.135115449991398</v>
+        <v>2.495747156034979</v>
       </c>
       <c r="C142">
-        <v>0.6577507843459672</v>
+        <v>0.7582275251578438</v>
       </c>
       <c r="D142">
-        <v>2.158135394226515</v>
+        <v>1.206218602417732</v>
       </c>
       <c r="E142">
-        <v>0.03091730660984989</v>
+        <v>0.2277332130536488</v>
       </c>
       <c r="F142">
-        <v>1.139224081211667</v>
+        <v>0.5646718597901171</v>
       </c>
       <c r="G142">
-        <v>15.00949643424941</v>
+        <v>11.03074955633852</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9311,32 +9311,32 @@
         </is>
       </c>
       <c r="O142">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B143">
-        <v>2.099411747978357</v>
+        <v>3.290641791245644</v>
       </c>
       <c r="C143">
-        <v>0.7152541592433693</v>
+        <v>1.206535615306193</v>
       </c>
       <c r="D143">
-        <v>1.036914187626247</v>
+        <v>0.9871922585373702</v>
       </c>
       <c r="E143">
-        <v>0.2997758512542271</v>
+        <v>0.323548396189419</v>
       </c>
       <c r="F143">
-        <v>0.5167401167282843</v>
+        <v>0.3092257355654985</v>
       </c>
       <c r="G143">
-        <v>8.529490056734137</v>
+        <v>35.01753622960902</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9374,32 +9374,32 @@
         </is>
       </c>
       <c r="O143">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B144">
-        <v>0.8899037455119601</v>
+        <v>1.809434464907629</v>
       </c>
       <c r="C144">
-        <v>0.5936162870271728</v>
+        <v>0.8491542323565293</v>
       </c>
       <c r="D144">
-        <v>-0.1964938896791465</v>
+        <v>0.6983588181407054</v>
       </c>
       <c r="E144">
-        <v>0.8442236147787927</v>
+        <v>0.4849528239273776</v>
       </c>
       <c r="F144">
-        <v>0.2780071304764667</v>
+        <v>0.3425637981652968</v>
       </c>
       <c r="G144">
-        <v>2.848591239077056</v>
+        <v>9.557498779295212</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9437,32 +9437,32 @@
         </is>
       </c>
       <c r="O144">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B145">
-        <v>3.944829667063196</v>
+        <v>6.377806955749759</v>
       </c>
       <c r="C145">
-        <v>0.698295031517814</v>
+        <v>1.230889042700221</v>
       </c>
       <c r="D145">
-        <v>1.96536666380945</v>
+        <v>1.505273210376142</v>
       </c>
       <c r="E145">
-        <v>0.04937181494339722</v>
+        <v>0.1322538497512808</v>
       </c>
       <c r="F145">
-        <v>1.003779789545706</v>
+        <v>0.5713953702218155</v>
       </c>
       <c r="G145">
-        <v>15.50308271218022</v>
+        <v>71.18787390422753</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9500,32 +9500,32 @@
         </is>
       </c>
       <c r="O145">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B146">
-        <v>2.094887592614914</v>
+        <v>2.708005621317973</v>
       </c>
       <c r="C146">
-        <v>0.6202230387138158</v>
+        <v>1.037946557633142</v>
       </c>
       <c r="D146">
-        <v>1.192312846668412</v>
+        <v>0.9597916420076665</v>
       </c>
       <c r="E146">
-        <v>0.2331385991206027</v>
+        <v>0.3371600896406658</v>
       </c>
       <c r="F146">
-        <v>0.6211920898788654</v>
+        <v>0.3541178753812501</v>
       </c>
       <c r="G146">
-        <v>7.064729408495352</v>
+        <v>20.70862544624321</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9563,32 +9563,32 @@
         </is>
       </c>
       <c r="O146">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B147">
-        <v>0.8664606309455379</v>
+        <v>1.696998100681006</v>
       </c>
       <c r="C147">
-        <v>0.5339583923707896</v>
+        <v>0.779612814569884</v>
       </c>
       <c r="D147">
-        <v>-0.2684452711600228</v>
+        <v>0.6783634865233381</v>
       </c>
       <c r="E147">
-        <v>0.78835659646929</v>
+        <v>0.4975412543446439</v>
       </c>
       <c r="F147">
-        <v>0.3042584349603683</v>
+        <v>0.3681914721339398</v>
       </c>
       <c r="G147">
-        <v>2.467487959951974</v>
+        <v>7.821480864356728</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9626,32 +9626,32 @@
         </is>
       </c>
       <c r="O147">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B148">
-        <v>4.107873726860769</v>
+        <v>5.190537361283517</v>
       </c>
       <c r="C148">
-        <v>0.6179154298099686</v>
+        <v>1.076995023590092</v>
       </c>
       <c r="D148">
-        <v>2.286567845828067</v>
+        <v>1.529103843161748</v>
       </c>
       <c r="E148">
-        <v>0.02222105983097171</v>
+        <v>0.1262387027801724</v>
       </c>
       <c r="F148">
-        <v>1.223619861674044</v>
+        <v>0.6287420334361404</v>
       </c>
       <c r="G148">
-        <v>13.79074260264676</v>
+        <v>42.85013036529622</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="O148">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="149">
@@ -9699,22 +9699,22 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.7964755246397053</v>
+        <v>0.7191151045083953</v>
       </c>
       <c r="C149">
-        <v>0.3914206288378393</v>
+        <v>0.3740086926036491</v>
       </c>
       <c r="D149">
-        <v>-0.5813665963849936</v>
+        <v>-0.8816208042092465</v>
       </c>
       <c r="E149">
-        <v>0.5609934054359058</v>
+        <v>0.377981900882593</v>
       </c>
       <c r="F149">
-        <v>0.3698235740068558</v>
+        <v>0.3454948949338176</v>
       </c>
       <c r="G149">
-        <v>1.71534024853249</v>
+        <v>1.496770404179721</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="O149">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="150">
@@ -9762,22 +9762,22 @@
         </is>
       </c>
       <c r="B150">
-        <v>0.8054234149044301</v>
+        <v>1.006769596816599</v>
       </c>
       <c r="C150">
-        <v>0.4573322961655243</v>
+        <v>0.4146137008175829</v>
       </c>
       <c r="D150">
-        <v>-0.4731508367324374</v>
+        <v>0.01627246270843064</v>
       </c>
       <c r="E150">
-        <v>0.6361055699425451</v>
+        <v>0.9870170262080866</v>
       </c>
       <c r="F150">
-        <v>0.3286565521058667</v>
+        <v>0.4466941551964191</v>
       </c>
       <c r="G150">
-        <v>1.973813919484413</v>
+        <v>2.269080553849127</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="O150">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="151">
@@ -9825,22 +9825,22 @@
         </is>
       </c>
       <c r="B151">
-        <v>1.045137179512669</v>
+        <v>0.7451944997717188</v>
       </c>
       <c r="C151">
-        <v>0.40144464395667</v>
+        <v>0.4107989786381775</v>
       </c>
       <c r="D151">
-        <v>0.1099731923861899</v>
+        <v>-0.7159463300815512</v>
       </c>
       <c r="E151">
-        <v>0.9124306353127898</v>
+        <v>0.4740244892957678</v>
       </c>
       <c r="F151">
-        <v>0.4758422463655355</v>
+        <v>0.3331170916690989</v>
       </c>
       <c r="G151">
-        <v>2.295533304036645</v>
+        <v>1.667025968879564</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9878,32 +9878,32 @@
         </is>
       </c>
       <c r="O151">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B152">
-        <v>1.190260548090324</v>
+        <v>1.008516346445382</v>
       </c>
       <c r="C152">
-        <v>0.5582046478576779</v>
+        <v>0.7963565723988284</v>
       </c>
       <c r="D152">
-        <v>0.3120221800397801</v>
+        <v>0.01064885661318577</v>
       </c>
       <c r="E152">
-        <v>0.7550236670085868</v>
+        <v>0.9915036022977319</v>
       </c>
       <c r="F152">
-        <v>0.3985633689611087</v>
+        <v>0.2117497949517643</v>
       </c>
       <c r="G152">
-        <v>3.554566933818045</v>
+        <v>4.803335093095293</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9941,32 +9941,32 @@
         </is>
       </c>
       <c r="O152">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B153">
-        <v>0.699578572667535</v>
+        <v>0.8548062801981527</v>
       </c>
       <c r="C153">
-        <v>0.5441060158735292</v>
+        <v>0.7046366405920725</v>
       </c>
       <c r="D153">
-        <v>-0.6566315274235669</v>
+        <v>-0.222640151742216</v>
       </c>
       <c r="E153">
-        <v>0.5114178717495157</v>
+        <v>0.8238155840971273</v>
       </c>
       <c r="F153">
-        <v>0.2408200369299861</v>
+        <v>0.2148225702249555</v>
       </c>
       <c r="G153">
-        <v>2.032265195100158</v>
+        <v>3.401382712724474</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10004,32 +10004,32 @@
         </is>
       </c>
       <c r="O153">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B154">
-        <v>1.71159114359591</v>
+        <v>1.384465089842944</v>
       </c>
       <c r="C154">
-        <v>0.5562335399911104</v>
+        <v>0.8315339908778231</v>
       </c>
       <c r="D154">
-        <v>0.9661830734146991</v>
+        <v>0.3912213473980742</v>
       </c>
       <c r="E154">
-        <v>0.3339525812007997</v>
+        <v>0.6956336303207367</v>
       </c>
       <c r="F154">
-        <v>0.5753514116470194</v>
+        <v>0.2713182410873554</v>
       </c>
       <c r="G154">
-        <v>5.091747727618755</v>
+        <v>7.064558495264253</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10067,32 +10067,32 @@
         </is>
       </c>
       <c r="O154">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B155">
-        <v>0.8291984605537779</v>
+        <v>0.7221017720153415</v>
       </c>
       <c r="C155">
-        <v>0.4272708684543591</v>
+        <v>0.4437335814299445</v>
       </c>
       <c r="D155">
-        <v>-0.4383536739672838</v>
+        <v>-0.7337492702350804</v>
       </c>
       <c r="E155">
-        <v>0.6611299229267804</v>
+        <v>0.463101563833169</v>
       </c>
       <c r="F155">
-        <v>0.3588928981745513</v>
+        <v>0.3026158711026849</v>
       </c>
       <c r="G155">
-        <v>1.91580856150112</v>
+        <v>1.723078724350059</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10130,32 +10130,32 @@
         </is>
       </c>
       <c r="O155">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B156">
-        <v>0.7311509696524299</v>
+        <v>0.8911177229009538</v>
       </c>
       <c r="C156">
-        <v>0.4640843917964455</v>
+        <v>0.450883869386518</v>
       </c>
       <c r="D156">
-        <v>-0.6747378736682367</v>
+        <v>-0.2556727876024609</v>
       </c>
       <c r="E156">
-        <v>0.4998423175434292</v>
+        <v>0.7982035092648037</v>
       </c>
       <c r="F156">
-        <v>0.294427051508424</v>
+        <v>0.368249389685318</v>
       </c>
       <c r="G156">
-        <v>1.815667879988919</v>
+        <v>2.156394058783803</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10193,32 +10193,32 @@
         </is>
       </c>
       <c r="O156">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B157">
-        <v>1.114441691234423</v>
+        <v>0.8001799457670159</v>
       </c>
       <c r="C157">
-        <v>0.4242563524100694</v>
+        <v>0.4878514718487436</v>
       </c>
       <c r="D157">
-        <v>0.2553964213887747</v>
+        <v>-0.4569395753878372</v>
       </c>
       <c r="E157">
-        <v>0.798416934487157</v>
+        <v>0.647714477414683</v>
       </c>
       <c r="F157">
-        <v>0.4852099394884147</v>
+        <v>0.3075585021221267</v>
       </c>
       <c r="G157">
-        <v>2.559676094992888</v>
+        <v>2.08184114953667</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
   </sheetData>
